--- a/src/test/resources/edit_password.xlsx
+++ b/src/test/resources/edit_password.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="12228" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,13 +130,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -606,148 +599,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/src/test/resources/edit_password.xlsx
+++ b/src/test/resources/edit_password.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12228" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +134,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -614,140 +620,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1122,218 +1131,221 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="43.2" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" ht="43.2" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="43.2" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" ht="86.4" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="57.6" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" ht="86.4" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" ht="86.4" spans="1:5">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="Hoa0987.team@gmail.com" tooltip="mailto:Hoa0987.team@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/src/test/resources/edit_password.xlsx
+++ b/src/test/resources/edit_password.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="26">
   <si>
     <t>Account</t>
   </si>
@@ -47,19 +47,16 @@
     <t>Hoa0987.team@gmail.com</t>
   </si>
   <si>
+    <t>saiMatKhau123</t>
+  </si>
+  <si>
+    <t>NewPass@2025</t>
+  </si>
+  <si>
+    <t>Nhập sai mật khẩu hiện tại</t>
+  </si>
+  <si>
     <t>abcd123456</t>
-  </si>
-  <si>
-    <t>NewPass@2025</t>
-  </si>
-  <si>
-    <t>Đổi mật khẩu thành công</t>
-  </si>
-  <si>
-    <t>saiMatKhau123</t>
-  </si>
-  <si>
-    <t>Nhập sai mật khẩu hiện tại</t>
   </si>
   <si>
     <t>NewPass@2026</t>
@@ -120,7 +117,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,12 +131,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -620,143 +611,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1107,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" ht="28.8" spans="1:5">
@@ -1127,225 +1115,205 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="57.6" spans="1:5">
+    <row r="2" ht="43.2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="43.2" spans="1:5">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="72" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="43.2" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="72" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" ht="43.2" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="43.2" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="43.2" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="72" spans="1:5">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="86.4" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="72" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="57.6" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="86.4" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" ht="72" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="86.4" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="72" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="57.6" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" ht="86.4" spans="1:5">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="14" ht="86.4" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="Hoa0987.team@gmail.com" tooltip="mailto:Hoa0987.team@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
